--- a/Prototyping/FirstPrototypeBOM.xlsx
+++ b/Prototyping/FirstPrototypeBOM.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="87">
   <si>
     <t>Component/Equipment Name</t>
   </si>
@@ -42,12 +43,6 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>SiC MOSFETs/IGBTs</t>
-  </si>
-  <si>
-    <t>1200V/1700V, 50A-200A range</t>
-  </si>
-  <si>
     <t>To Be Ordered</t>
   </si>
   <si>
@@ -57,39 +52,12 @@
     <t>Critical for prototyping</t>
   </si>
   <si>
-    <t>Diodes (Schottky/Freewheeling)</t>
-  </si>
-  <si>
-    <t>High-speed and efficient diodes</t>
-  </si>
-  <si>
-    <t>Vishay</t>
-  </si>
-  <si>
-    <t>High efficiency required</t>
-  </si>
-  <si>
-    <t>Gate Driver ICs</t>
-  </si>
-  <si>
-    <t>For MOSFETs/IGBTs</t>
-  </si>
-  <si>
-    <t>Ordered</t>
-  </si>
-  <si>
-    <t>Texas Instruments</t>
-  </si>
-  <si>
     <t>Essential for switching</t>
   </si>
   <si>
     <t>Current Sensors</t>
   </si>
   <si>
-    <t>For current monitoring (e.g., LEM LA 55-P)</t>
-  </si>
-  <si>
     <t>LEM</t>
   </si>
   <si>
@@ -99,18 +67,12 @@
     <t>Voltage Sensors</t>
   </si>
   <si>
-    <t>DC-Link voltage monitoring (e.g., LV25-P)</t>
-  </si>
-  <si>
     <t>Critical for system monitoring</t>
   </si>
   <si>
     <t>DC-Link Capacitors</t>
   </si>
   <si>
-    <t>High voltage film capacitors (1000µF, 1200V)</t>
-  </si>
-  <si>
     <t>In Stock</t>
   </si>
   <si>
@@ -132,78 +94,30 @@
     <t>Optimized for low inductance</t>
   </si>
   <si>
-    <t>Inductors/Filters</t>
-  </si>
-  <si>
-    <t>For EMI and harmonic reduction</t>
-  </si>
-  <si>
-    <t>Würth Elektronik</t>
-  </si>
-  <si>
-    <t>Custom design may be needed</t>
-  </si>
-  <si>
-    <t>Resistors</t>
-  </si>
-  <si>
-    <t>High power resistors for pre-charge circuit</t>
-  </si>
-  <si>
-    <t>Ensure high power tolerance</t>
-  </si>
-  <si>
     <t>Snubber Capacitors</t>
   </si>
   <si>
     <t>Dampen switching transients</t>
   </si>
   <si>
-    <t>Murata</t>
-  </si>
-  <si>
     <t>Minimize voltage spikes</t>
   </si>
   <si>
     <t>Microcontroller/DSP</t>
   </si>
   <si>
-    <t>For control algorithms (e.g., TI TMS320F28379D)</t>
-  </si>
-  <si>
     <t>Critical for algorithm testing</t>
   </si>
   <si>
-    <t>FPGA</t>
-  </si>
-  <si>
-    <t>For fast PWM generation (e.g., Xilinx Zynq)</t>
-  </si>
-  <si>
-    <t>Xilinx</t>
-  </si>
-  <si>
-    <t>Required for advanced control</t>
-  </si>
-  <si>
     <t>Temperature Sensors</t>
   </si>
   <si>
-    <t>Thermal monitoring (e.g., NTC/PTC thermistors)</t>
-  </si>
-  <si>
-    <t>EPCOS</t>
-  </si>
-  <si>
     <t>Ensure temperature stability</t>
   </si>
   <si>
     <t>Overvoltage Protection Circuitry</t>
   </si>
   <si>
-    <t>Protect against overvoltage conditions</t>
-  </si>
-  <si>
     <t>For overvoltage events</t>
   </si>
   <si>
@@ -216,15 +130,9 @@
     <t>Critical for control and power separation</t>
   </si>
   <si>
-    <t>Heatsinks</t>
-  </si>
-  <si>
     <t>For semiconductor cooling</t>
   </si>
   <si>
-    <t>Fischer Elektronik</t>
-  </si>
-  <si>
     <t>Match cooling requirements</t>
   </si>
   <si>
@@ -234,72 +142,27 @@
     <t>Between heatsink and semiconductors</t>
   </si>
   <si>
-    <t>3M</t>
-  </si>
-  <si>
     <t>Ensure high thermal conductivity</t>
   </si>
   <si>
-    <t>Liquid Cooling Plates</t>
-  </si>
-  <si>
-    <t>For high-power designs</t>
-  </si>
-  <si>
-    <t>For high power density systems</t>
-  </si>
-  <si>
-    <t>Fans</t>
-  </si>
-  <si>
-    <t>For air cooling requirements</t>
-  </si>
-  <si>
-    <t>Noctua</t>
-  </si>
-  <si>
-    <t>Ensure adequate airflow</t>
-  </si>
-  <si>
     <t>Oscilloscope</t>
   </si>
   <si>
     <t>For waveform analysis</t>
   </si>
   <si>
-    <t>Tektronix</t>
-  </si>
-  <si>
-    <t>Function Generator</t>
-  </si>
-  <si>
-    <t>For PWM and signal generation</t>
-  </si>
-  <si>
-    <t>Keysight</t>
-  </si>
-  <si>
-    <t>Critical for testing</t>
-  </si>
-  <si>
     <t>LCR Meter</t>
   </si>
   <si>
     <t>For passive component measurements</t>
   </si>
   <si>
-    <t>Precise measurement needed</t>
-  </si>
-  <si>
     <t>Power Analyzer</t>
   </si>
   <si>
     <t>For efficiency testing</t>
   </si>
   <si>
-    <t>Yokogawa</t>
-  </si>
-  <si>
     <t>Critical for system efficiency</t>
   </si>
   <si>
@@ -312,24 +175,12 @@
     <t>Ensure compatibility</t>
   </si>
   <si>
-    <t>EMI Test Setup</t>
-  </si>
-  <si>
-    <t>For EMI analysis and compliance</t>
-  </si>
-  <si>
-    <t>Essential for compliance</t>
-  </si>
-  <si>
     <t>Connectors</t>
   </si>
   <si>
     <t>High current and voltage connectors</t>
   </si>
   <si>
-    <t>Amphenol</t>
-  </si>
-  <si>
     <t>High reliability needed</t>
   </si>
   <si>
@@ -342,41 +193,113 @@
     <t>Custom design may be required</t>
   </si>
   <si>
-    <t>PCB (Printed Circuit Board)</t>
-  </si>
-  <si>
-    <t>For control circuit design</t>
-  </si>
-  <si>
-    <t>Critical for PCB testing</t>
-  </si>
-  <si>
-    <t>Enclosure</t>
-  </si>
-  <si>
-    <t>EMI shielding and physical protection</t>
-  </si>
-  <si>
-    <t>Ensure EMI shielding</t>
-  </si>
-  <si>
     <t>Fuses/Circuit Breakers</t>
   </si>
   <si>
     <t>For circuit protection</t>
   </si>
   <si>
-    <t>Eaton</t>
-  </si>
-  <si>
     <t>Critical for circuit protection</t>
+  </si>
+  <si>
+    <t>2kV 62mm Power Module</t>
+  </si>
+  <si>
+    <t>Gate Driver Ics</t>
+  </si>
+  <si>
+    <t>For SiC  MOSFETs (at least 1500V)</t>
+  </si>
+  <si>
+    <t>For current monitoring (e.g., LEM LF 310-S)</t>
+  </si>
+  <si>
+    <t>https://www.lem.com/en/product-list/lf-310s</t>
+  </si>
+  <si>
+    <t>https://www.accuenergy.com/products/hv2-dc-voltage-sensor/?utm_source=chatgpt.com</t>
+  </si>
+  <si>
+    <t>DC-Link voltage monitoring (e.g., DVL 1500-UI)</t>
+  </si>
+  <si>
+    <t>To be ordered</t>
+  </si>
+  <si>
+    <t>High voltage film capacitors (200µF, 1300V- C44U)</t>
+  </si>
+  <si>
+    <t>Cornell Dubilier-CDE</t>
+  </si>
+  <si>
+    <t>https://www.mouser.se/ProductDetail/Cornell-Dubilier-CDE/SCD105K162A3Z25-F?qs=59Iuwm0WYIi7PFxKkjFJtg%3D%3D&amp;srsltid=AfmBOoqS60oh50cgeFOKdh_Q2G4ZsFBuBlZ6EXEBZhpKEFhGAWeO2Euy&amp;_gl=1*1i2vxz7*_ga*MTM1NTQ4MTUzNy4xNzM2NDE4NzMw*_ga_15W4STQT4T*MTczNjQxODczMC4xLjEuMTczNjQxODc4Mi44LjAuMA..</t>
+  </si>
+  <si>
+    <t>For control algorithms (e.g., Imperix B-Box RCP)</t>
+  </si>
+  <si>
+    <t>Imperix</t>
+  </si>
+  <si>
+    <t>Thermal monitoring (e.g., NTC thermistors)</t>
+  </si>
+  <si>
+    <t>https://www.digikey.se/sv/products/detail/epcos-tdk-electronics/B57861S0302F040/739892?srsltid=AfmBOoqdkyqw8YD06O3VHpVQNA-xPYOicwH9flon-MyoWAiy6Xsg_IyU</t>
+  </si>
+  <si>
+    <t>EPCOS-TDK Electronics</t>
+  </si>
+  <si>
+    <t>Protect against overvoltage conditions (TVS)</t>
+  </si>
+  <si>
+    <t>a. Snubber + TVS Combination</t>
+  </si>
+  <si>
+    <r>
+      <t>Circuit Components</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <t>Snubber Capacitor: KEMET C4AQ Series, 2000V, 0.22 µF.</t>
+  </si>
+  <si>
+    <t>Snubber Resistor: Vishay CPF 10Ω, 5W.</t>
+  </si>
+  <si>
+    <t>TVS Diode: Littelfuse SMCJ1500CA.</t>
+  </si>
+  <si>
+    <t>Liquid Cooling</t>
+  </si>
+  <si>
+    <t>Cold Plate</t>
+  </si>
+  <si>
+    <t>Ensure adequate liquidflow</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>SiC MOSFETs</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -397,13 +320,64 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="10">
@@ -526,18 +500,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -546,38 +519,49 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Bad" xfId="2" builtinId="27"/>
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="15">
     <dxf>
       <font>
         <b/>
@@ -595,7 +579,7 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -604,6 +588,12 @@
         </right>
         <top/>
         <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -619,7 +609,7 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -630,6 +620,12 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -645,7 +641,7 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -658,6 +654,12 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -673,7 +675,7 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -686,6 +688,12 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -701,7 +709,7 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -714,6 +722,12 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -729,7 +743,7 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -742,6 +756,12 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -757,7 +777,7 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -770,6 +790,12 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -785,7 +811,41 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="thin">
           <color indexed="64"/>
@@ -793,27 +853,33 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -857,32 +923,18 @@
       </border>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -898,9 +950,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:G31" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" headerRowBorderDxfId="10" tableBorderDxfId="11" totalsRowBorderDxfId="9">
-  <autoFilter ref="A1:G31"/>
-  <tableColumns count="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:H22" totalsRowShown="0" headerRowDxfId="0" dataDxfId="14" headerRowBorderDxfId="10" tableBorderDxfId="11" totalsRowBorderDxfId="9">
+  <autoFilter ref="A1:H22"/>
+  <tableColumns count="8">
     <tableColumn id="1" name="Component/Equipment Name" dataDxfId="8"/>
     <tableColumn id="2" name="Description" dataDxfId="7"/>
     <tableColumn id="3" name="Quantity Needed" dataDxfId="6"/>
@@ -908,6 +960,7 @@
     <tableColumn id="5" name="Status" dataDxfId="4"/>
     <tableColumn id="6" name="Supplier" dataDxfId="3"/>
     <tableColumn id="7" name="Notes" dataDxfId="2"/>
+    <tableColumn id="9" name="Link" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1176,20 +1229,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="59.5703125" style="10" customWidth="1"/>
-    <col min="2" max="2" width="51.5703125" style="10" customWidth="1"/>
-    <col min="3" max="3" width="19.42578125" style="10" customWidth="1"/>
-    <col min="4" max="4" width="24.140625" style="10" customWidth="1"/>
-    <col min="5" max="5" width="18" style="10" customWidth="1"/>
-    <col min="6" max="6" width="19.28515625" style="10" customWidth="1"/>
-    <col min="7" max="7" width="42.140625" style="10" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="10"/>
+    <col min="1" max="1" width="59.5703125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="51.5703125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="24.140625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="18" style="6" customWidth="1"/>
+    <col min="6" max="6" width="24.85546875" style="6" customWidth="1"/>
+    <col min="7" max="7" width="42.140625" style="6" customWidth="1"/>
+    <col min="8" max="8" width="80.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1208,702 +1262,477 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="H1" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="I1" s="14"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" s="4">
+        <v>6</v>
+      </c>
+      <c r="D2" s="4">
+        <v>9</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="17"/>
+      <c r="I2" s="15"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="17"/>
+      <c r="I3" s="15"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="4">
+        <v>3</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="F4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="I4" s="15"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="4">
+        <v>1</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="I5" s="15"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="4">
+        <v>5</v>
+      </c>
+      <c r="D6" s="4">
         <v>8</v>
       </c>
-      <c r="C2" s="5">
-        <v>10</v>
-      </c>
-      <c r="D2" s="5">
-        <v>5</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="5">
+      <c r="E6" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="17"/>
+      <c r="I6" s="15"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="5">
-        <v>10</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="B7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="4">
+        <v>2</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="5">
-        <v>10</v>
-      </c>
-      <c r="D4" s="5">
+      <c r="F7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="17"/>
+      <c r="I7" s="15"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="4">
+        <v>6</v>
+      </c>
+      <c r="D8" s="4">
         <v>0</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="E8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="I8" s="15"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="4">
+        <v>1</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" s="17"/>
+      <c r="I9" s="15"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" s="4">
+        <v>6</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="I10" s="15"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C11" s="4">
+        <v>1</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="5">
+      <c r="G11" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" s="17"/>
+      <c r="I11" s="15"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="4">
+        <v>2</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" s="17"/>
+      <c r="I12" s="15"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="4">
+        <v>1</v>
+      </c>
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" s="17"/>
+      <c r="I13" s="15"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="4">
         <v>6</v>
       </c>
-      <c r="D5" s="5">
-        <v>3</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="5">
-        <v>6</v>
-      </c>
-      <c r="D6" s="5">
-        <v>2</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="5">
-        <v>4</v>
-      </c>
-      <c r="D7" s="5">
-        <v>2</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="5">
-        <v>2</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H14" s="17"/>
+      <c r="I14" s="15"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4">
         <v>1</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="5">
-        <v>4</v>
-      </c>
-      <c r="D9" s="5">
-        <v>2</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="D15" s="4">
+        <v>0</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="H15" s="17"/>
+      <c r="I15" s="15"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="5">
-        <v>6</v>
-      </c>
-      <c r="D10" s="5">
-        <v>3</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" s="6" t="s">
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H16" s="17"/>
+      <c r="I16" s="15"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="B17" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="15"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="5">
-        <v>6</v>
-      </c>
-      <c r="D11" s="5">
-        <v>2</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="5" t="s">
+      <c r="B18" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="H18" s="17"/>
+      <c r="I18" s="15"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B19" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="5">
-        <v>2</v>
-      </c>
-      <c r="D12" s="5">
-        <v>0</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="6" t="s">
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="H19" s="17"/>
+      <c r="I19" s="15"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B20" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C13" s="5">
-        <v>2</v>
-      </c>
-      <c r="D13" s="5">
-        <v>0</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F13" s="5" t="s">
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="H20" s="17"/>
+      <c r="I20" s="15"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+      <c r="B21" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="5">
-        <v>6</v>
-      </c>
-      <c r="D14" s="5">
-        <v>3</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" s="5" t="s">
+      <c r="H21" s="17"/>
+      <c r="I21" s="15"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="B22" s="5" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C15" s="5">
-        <v>4</v>
-      </c>
-      <c r="D15" s="5">
-        <v>1</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C16" s="5">
-        <v>2</v>
-      </c>
-      <c r="D16" s="5">
-        <v>1</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C17" s="5">
-        <v>4</v>
-      </c>
-      <c r="D17" s="5">
-        <v>2</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C18" s="5">
-        <v>6</v>
-      </c>
-      <c r="D18" s="5">
-        <v>3</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" s="5">
-        <v>2</v>
-      </c>
-      <c r="D19" s="5">
-        <v>0</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C20" s="5">
-        <v>4</v>
-      </c>
-      <c r="D20" s="5">
-        <v>2</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C21" s="5">
-        <v>1</v>
-      </c>
-      <c r="D21" s="5">
-        <v>1</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C22" s="5">
-        <v>1</v>
-      </c>
-      <c r="D22" s="5">
-        <v>1</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="C23" s="5">
-        <v>1</v>
-      </c>
-      <c r="D23" s="5">
-        <v>1</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C24" s="5">
-        <v>1</v>
-      </c>
-      <c r="D24" s="5">
-        <v>1</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="C25" s="5">
-        <v>1</v>
-      </c>
-      <c r="D25" s="5">
-        <v>1</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C26" s="5">
-        <v>1</v>
-      </c>
-      <c r="D26" s="5">
-        <v>1</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C27" s="5">
-        <v>10</v>
-      </c>
-      <c r="D27" s="5">
-        <v>5</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C28" s="5">
-        <v>20</v>
-      </c>
-      <c r="D28" s="5">
-        <v>10</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C29" s="5">
-        <v>10</v>
-      </c>
-      <c r="D29" s="5">
-        <v>5</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C30" s="5">
-        <v>1</v>
-      </c>
-      <c r="D30" s="5">
-        <v>1</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="C31" s="8">
-        <v>4</v>
-      </c>
-      <c r="D31" s="8">
-        <v>2</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="G31" s="9" t="s">
-        <v>116</v>
-      </c>
+      <c r="H22" s="18"/>
+      <c r="I22" s="15"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:G31">
+  <conditionalFormatting sqref="A1:H22">
     <cfRule type="expression" dxfId="13" priority="2">
       <formula>"$A$1:$G$31"</formula>
     </cfRule>
@@ -1919,4 +1748,45 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="53.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="10"/>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Prototyping/FirstPrototypeBOM.xlsx
+++ b/Prototyping/FirstPrototypeBOM.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="92">
   <si>
     <t>Component/Equipment Name</t>
   </si>
@@ -215,9 +215,6 @@
   </si>
   <si>
     <t>https://www.lem.com/en/product-list/lf-310s</t>
-  </si>
-  <si>
-    <t>https://www.accuenergy.com/products/hv2-dc-voltage-sensor/?utm_source=chatgpt.com</t>
   </si>
   <si>
     <t>DC-Link voltage monitoring (e.g., DVL 1500-UI)</t>
@@ -294,12 +291,30 @@
   <si>
     <t>SiC MOSFETs</t>
   </si>
+  <si>
+    <t>https://www.accuenergy.com/products/hv2-dc-voltage-sensor/</t>
+  </si>
+  <si>
+    <t>https://www.infineon.com/cms/en/product/power/gate-driver-ics/1ed3890mc12m/#!designsupport</t>
+  </si>
+  <si>
+    <t>Imperix VHDCI Breakout PCB</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/Electronics-Salon-68-Pin-SCSI-5-Terminal-Breakout/dp/B07C9X68G6</t>
+  </si>
+  <si>
+    <t>https://se.farnell.com/ni/785633-01/vhdci-connector-68-pin-r-a-tht/dp/3622789?gross_price=true&amp;CMP=KNC-GSE-GEN-Shopping-Pmax-High-ROAS&amp;mckv=_dc|pcrid||&amp;gad_source=1&amp;gclid=CjwKCAiAiaC-BhBEEiwAjY99qOujcMV8-8jrrJwTcc46v-AvITfLAboAL8qO4t8aKMm0DDaEuoLnFBoCJbMQAvD_BwE</t>
+  </si>
+  <si>
+    <t>VHDCI HD68</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -361,6 +376,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -500,12 +523,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -555,351 +579,43 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
     <cellStyle name="Good" xfId="1" builtinId="26"/>
+    <cellStyle name="Hyperlink" xfId="3" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="17">
     <dxf>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <fill>
@@ -935,6 +651,366 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -950,17 +1026,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:H22" totalsRowShown="0" headerRowDxfId="0" dataDxfId="14" headerRowBorderDxfId="10" tableBorderDxfId="11" totalsRowBorderDxfId="9">
-  <autoFilter ref="A1:H22"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:H24" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13" headerRowBorderDxfId="11" tableBorderDxfId="12" totalsRowBorderDxfId="10">
+  <autoFilter ref="A1:H24"/>
   <tableColumns count="8">
-    <tableColumn id="1" name="Component/Equipment Name" dataDxfId="8"/>
-    <tableColumn id="2" name="Description" dataDxfId="7"/>
-    <tableColumn id="3" name="Quantity Needed" dataDxfId="6"/>
-    <tableColumn id="4" name="Available Quantity" dataDxfId="5"/>
-    <tableColumn id="5" name="Status" dataDxfId="4"/>
-    <tableColumn id="6" name="Supplier" dataDxfId="3"/>
-    <tableColumn id="7" name="Notes" dataDxfId="2"/>
-    <tableColumn id="9" name="Link" dataDxfId="1"/>
+    <tableColumn id="1" name="Component/Equipment Name" dataDxfId="9"/>
+    <tableColumn id="2" name="Description" dataDxfId="8"/>
+    <tableColumn id="3" name="Quantity Needed" dataDxfId="7"/>
+    <tableColumn id="4" name="Available Quantity" dataDxfId="6"/>
+    <tableColumn id="5" name="Status" dataDxfId="5"/>
+    <tableColumn id="6" name="Supplier" dataDxfId="4"/>
+    <tableColumn id="7" name="Notes" dataDxfId="3"/>
+    <tableColumn id="9" name="Link" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1229,7 +1305,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="59.5703125" style="6" customWidth="1"/>
@@ -1266,13 +1342,13 @@
         <v>6</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I1" s="14"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>60</v>
@@ -1311,7 +1387,9 @@
       <c r="G3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="17"/>
+      <c r="H3" s="17" t="s">
+        <v>87</v>
+      </c>
       <c r="I3" s="15"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -1336,7 +1414,7 @@
       <c r="G4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="17" t="s">
+      <c r="H4" s="19" t="s">
         <v>64</v>
       </c>
       <c r="I4" s="15"/>
@@ -1346,7 +1424,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C5" s="4">
         <v>1</v>
@@ -1363,8 +1441,8 @@
       <c r="G5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="17" t="s">
-        <v>65</v>
+      <c r="H5" s="19" t="s">
+        <v>86</v>
       </c>
       <c r="I5" s="15"/>
     </row>
@@ -1373,7 +1451,7 @@
         <v>16</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C6" s="4">
         <v>5</v>
@@ -1382,7 +1460,7 @@
         <v>8</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>18</v>
@@ -1435,13 +1513,13 @@
         <v>7</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>26</v>
       </c>
       <c r="H8" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I8" s="15"/>
     </row>
@@ -1450,7 +1528,7 @@
         <v>27</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C9" s="4">
         <v>1</v>
@@ -1462,7 +1540,7 @@
         <v>17</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>28</v>
@@ -1475,7 +1553,7 @@
         <v>29</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C10" s="4">
         <v>6</v>
@@ -1487,13 +1565,13 @@
         <v>7</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>30</v>
       </c>
       <c r="H10" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I10" s="15"/>
     </row>
@@ -1502,7 +1580,7 @@
         <v>31</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C11" s="4">
         <v>1</v>
@@ -1549,7 +1627,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>36</v>
@@ -1561,7 +1639,7 @@
         <v>1</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>22</v>
@@ -1585,9 +1663,7 @@
       <c r="D14" s="4">
         <v>0</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>7</v>
-      </c>
+      <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4" t="s">
         <v>40</v>
@@ -1597,7 +1673,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4">
@@ -1609,7 +1685,7 @@
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H15" s="17"/>
       <c r="I15" s="15"/>
@@ -1731,21 +1807,53 @@
       <c r="H22" s="18"/>
       <c r="I22" s="15"/>
     </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="18" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="18" t="s">
+        <v>90</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:H22">
-    <cfRule type="expression" dxfId="13" priority="2">
+  <conditionalFormatting sqref="A1:H24">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>"$A$1:$G$31"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="16" priority="1">
       <formula>"$A$1:$G$31"</formula>
     </cfRule>
   </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="H5" r:id="rId1"/>
+    <hyperlink ref="H4" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1760,7 +1868,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -1768,22 +1876,22 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/Prototyping/FirstPrototypeBOM.xlsx
+++ b/Prototyping/FirstPrototypeBOM.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="98">
   <si>
     <t>Component/Equipment Name</t>
   </si>
@@ -308,6 +308,24 @@
   </si>
   <si>
     <t>VHDCI HD68</t>
+  </si>
+  <si>
+    <t>https://se.rs-online.com/web/p/dc-dc-converters/8289040</t>
+  </si>
+  <si>
+    <t>Isolated DC-DC supply</t>
+  </si>
+  <si>
+    <t>Opamp Isolation</t>
+  </si>
+  <si>
+    <t>https://www.ti.com/product/ISO224</t>
+  </si>
+  <si>
+    <t>https://www.ti.com/lit/an/sbaa321a/sbaa321a.pdf?ts=1743507065660&amp;ref_url=https%253A%252F%252Fwww.google.com%252F</t>
+  </si>
+  <si>
+    <t>https://docs.rs-online.com/4e7c/A700000007009511.pdf</t>
   </si>
 </sst>
 </file>
@@ -529,7 +547,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -588,6 +606,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -595,28 +616,7 @@
     <cellStyle name="Hyperlink" xfId="3" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="16">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -986,6 +986,13 @@
     </dxf>
     <dxf>
       <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
         <patternFill patternType="solid">
           <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
@@ -1005,13 +1012,6 @@
         </bottom>
       </border>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1026,17 +1026,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:H24" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13" headerRowBorderDxfId="11" tableBorderDxfId="12" totalsRowBorderDxfId="10">
-  <autoFilter ref="A1:H24"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:H28" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12" headerRowBorderDxfId="10" tableBorderDxfId="11" totalsRowBorderDxfId="9">
+  <autoFilter ref="A1:H28"/>
   <tableColumns count="8">
-    <tableColumn id="1" name="Component/Equipment Name" dataDxfId="9"/>
-    <tableColumn id="2" name="Description" dataDxfId="8"/>
-    <tableColumn id="3" name="Quantity Needed" dataDxfId="7"/>
-    <tableColumn id="4" name="Available Quantity" dataDxfId="6"/>
-    <tableColumn id="5" name="Status" dataDxfId="5"/>
-    <tableColumn id="6" name="Supplier" dataDxfId="4"/>
-    <tableColumn id="7" name="Notes" dataDxfId="3"/>
-    <tableColumn id="9" name="Link" dataDxfId="2"/>
+    <tableColumn id="1" name="Component/Equipment Name" dataDxfId="8"/>
+    <tableColumn id="2" name="Description" dataDxfId="7"/>
+    <tableColumn id="3" name="Quantity Needed" dataDxfId="6"/>
+    <tableColumn id="4" name="Available Quantity" dataDxfId="5"/>
+    <tableColumn id="5" name="Status" dataDxfId="4"/>
+    <tableColumn id="6" name="Supplier" dataDxfId="3"/>
+    <tableColumn id="7" name="Notes" dataDxfId="2"/>
+    <tableColumn id="9" name="Link" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1305,7 +1305,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="59.5703125" style="6" customWidth="1"/>
@@ -1371,7 +1371,7 @@
       <c r="H2" s="17"/>
       <c r="I2" s="15"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>61</v>
       </c>
@@ -1387,7 +1387,7 @@
       <c r="G3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="H3" s="19" t="s">
         <v>87</v>
       </c>
       <c r="I3" s="15"/>
@@ -1496,7 +1496,7 @@
       <c r="H7" s="17"/>
       <c r="I7" s="15"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>24</v>
       </c>
@@ -1518,7 +1518,7 @@
       <c r="G8" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H8" s="17" t="s">
+      <c r="H8" s="19" t="s">
         <v>69</v>
       </c>
       <c r="I8" s="15"/>
@@ -1548,7 +1548,7 @@
       <c r="H9" s="17"/>
       <c r="I9" s="15"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>29</v>
       </c>
@@ -1570,7 +1570,7 @@
       <c r="G10" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="H10" s="17" t="s">
+      <c r="H10" s="19" t="s">
         <v>73</v>
       </c>
       <c r="I10" s="15"/>
@@ -1807,7 +1807,7 @@
       <c r="H22" s="18"/>
       <c r="I22" s="15"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="20" t="s">
         <v>88</v>
       </c>
@@ -1817,11 +1817,11 @@
       <c r="E23" s="21"/>
       <c r="F23" s="21"/>
       <c r="G23" s="21"/>
-      <c r="H23" s="18" t="s">
+      <c r="H23" s="22" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="20" t="s">
         <v>91</v>
       </c>
@@ -1831,29 +1831,89 @@
       <c r="E24" s="21"/>
       <c r="F24" s="21"/>
       <c r="G24" s="21"/>
-      <c r="H24" s="18" t="s">
+      <c r="H24" s="22" t="s">
         <v>90</v>
       </c>
     </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="20"/>
+      <c r="B25" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="22" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="20"/>
+      <c r="B26" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="18" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A27" s="20"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="18" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="20"/>
+      <c r="B28" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="18" t="s">
+        <v>97</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:H24">
-    <cfRule type="expression" dxfId="1" priority="2">
+  <conditionalFormatting sqref="A1:H28">
+    <cfRule type="expression" dxfId="15" priority="2">
       <formula>"$A$1:$G$31"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="expression" dxfId="16" priority="1">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>"$A$1:$G$31"</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="H5" r:id="rId1"/>
     <hyperlink ref="H4" r:id="rId2"/>
+    <hyperlink ref="H3" r:id="rId3" location="!designsupport"/>
+    <hyperlink ref="H8" display="https://www.mouser.se/ProductDetail/Cornell-Dubilier-CDE/SCD105K162A3Z25-F?qs=59Iuwm0WYIi7PFxKkjFJtg%3D%3D&amp;srsltid=AfmBOoqS60oh50cgeFOKdh_Q2G4ZsFBuBlZ6EXEBZhpKEFhGAWeO2Euy&amp;_gl=1*1i2vxz7*_ga*MTM1NTQ4MTUzNy4xNzM2NDE4NzMw*_ga_15W4STQT4T*MTczNjQxODczMC4xLjEuM"/>
+    <hyperlink ref="H10" r:id="rId4"/>
+    <hyperlink ref="H24" display="https://se.farnell.com/ni/785633-01/vhdci-connector-68-pin-r-a-tht/dp/3622789?gross_price=true&amp;CMP=KNC-GSE-GEN-Shopping-Pmax-High-ROAS&amp;mckv=_dc|pcrid||&amp;gad_source=1&amp;gclid=CjwKCAiAiaC-BhBEEiwAjY99qOujcMV8-8jrrJwTcc46v-AvITfLAboAL8qO4t8aKMm0DDaEuoLnFBoCJbMQ"/>
+    <hyperlink ref="H25" r:id="rId5"/>
+    <hyperlink ref="H23" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
   <tableParts count="1">
-    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId8"/>
   </tableParts>
 </worksheet>
 </file>

--- a/Prototyping/FirstPrototypeBOM.xlsx
+++ b/Prototyping/FirstPrototypeBOM.xlsx
@@ -616,28 +616,7 @@
     <cellStyle name="Hyperlink" xfId="3" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="15">
     <dxf>
       <font>
         <strike val="0"/>
@@ -914,13 +893,6 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -949,6 +921,13 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1026,17 +1005,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:H28" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12" headerRowBorderDxfId="10" tableBorderDxfId="11" totalsRowBorderDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:H28" totalsRowShown="0" headerRowDxfId="12" dataDxfId="10" headerRowBorderDxfId="11" tableBorderDxfId="9" totalsRowBorderDxfId="8">
   <autoFilter ref="A1:H28"/>
   <tableColumns count="8">
-    <tableColumn id="1" name="Component/Equipment Name" dataDxfId="8"/>
-    <tableColumn id="2" name="Description" dataDxfId="7"/>
-    <tableColumn id="3" name="Quantity Needed" dataDxfId="6"/>
-    <tableColumn id="4" name="Available Quantity" dataDxfId="5"/>
-    <tableColumn id="5" name="Status" dataDxfId="4"/>
-    <tableColumn id="6" name="Supplier" dataDxfId="3"/>
-    <tableColumn id="7" name="Notes" dataDxfId="2"/>
-    <tableColumn id="9" name="Link" dataDxfId="1"/>
+    <tableColumn id="1" name="Component/Equipment Name" dataDxfId="7"/>
+    <tableColumn id="2" name="Description" dataDxfId="6"/>
+    <tableColumn id="3" name="Quantity Needed" dataDxfId="5"/>
+    <tableColumn id="4" name="Available Quantity" dataDxfId="4"/>
+    <tableColumn id="5" name="Status" dataDxfId="3"/>
+    <tableColumn id="6" name="Supplier" dataDxfId="2"/>
+    <tableColumn id="7" name="Notes" dataDxfId="1"/>
+    <tableColumn id="9" name="Link" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1885,18 +1864,18 @@
       <c r="E28" s="21"/>
       <c r="F28" s="21"/>
       <c r="G28" s="21"/>
-      <c r="H28" s="18" t="s">
+      <c r="H28" s="22" t="s">
         <v>97</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:H28">
-    <cfRule type="expression" dxfId="15" priority="2">
+    <cfRule type="expression" dxfId="14" priority="2">
       <formula>"$A$1:$G$31"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>"$A$1:$G$31"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1909,11 +1888,12 @@
     <hyperlink ref="H24" display="https://se.farnell.com/ni/785633-01/vhdci-connector-68-pin-r-a-tht/dp/3622789?gross_price=true&amp;CMP=KNC-GSE-GEN-Shopping-Pmax-High-ROAS&amp;mckv=_dc|pcrid||&amp;gad_source=1&amp;gclid=CjwKCAiAiaC-BhBEEiwAjY99qOujcMV8-8jrrJwTcc46v-AvITfLAboAL8qO4t8aKMm0DDaEuoLnFBoCJbMQ"/>
     <hyperlink ref="H25" r:id="rId5"/>
     <hyperlink ref="H23" r:id="rId6"/>
+    <hyperlink ref="H28" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>
   <tableParts count="1">
-    <tablePart r:id="rId8"/>
+    <tablePart r:id="rId9"/>
   </tableParts>
 </worksheet>
 </file>
